--- a/registration_forms/016_murder_mystery_event_registration--registration_forms.xlsx
+++ b/registration_forms/016_murder_mystery_event_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Confirm participation</t>
+          <t>Confirm Participation Hint</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Confirm participation</t>
+          <t>Confirm Participation Label</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Confirm participation</t>
+          <t>Confirm Participation Label Hint</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Participant status</t>
+          <t>Participant Status Hint</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Participant status</t>
+          <t>Participant Status Label</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Participant status</t>
+          <t>Participant Status Label Hint</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'actor',_'value':_'actor'}</t>
+          <t>actor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Actor', 'value': 'actor'}</t>
+          <t>Actor</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'director',_'value':_'director'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Director', 'value': 'director'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'producer',_'value':_'producer'}</t>
+          <t>producer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Producer', 'value': 'producer'}</t>
+          <t>Producer</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open', 'value': 'open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'attending',_'value':_'attending'}</t>
+          <t>attending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Attending', 'value': 'attending'}</t>
+          <t>Attending</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_attending',_'value':_'not_attending'}</t>
+          <t>not_attending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Attending', 'value': 'not_attending'}</t>
+          <t>Not Attending</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'attending',_'value':_'attending'}</t>
+          <t>attending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Attending', 'value': 'attending'}</t>
+          <t>Attending</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_attending',_'value':_'not_attending'}</t>
+          <t>not_attending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Attending', 'value': 'not_attending'}</t>
+          <t>Not Attending</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
